--- a/pregenereated_results/s2/ate_evalue_survey.xlsx
+++ b/pregenereated_results/s2/ate_evalue_survey.xlsx
@@ -501,7 +501,7 @@
         <v>2.450526729395442</v>
       </c>
       <c r="F2" t="n">
-        <v>2.013998684568711</v>
+        <v>2.013998684568712</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.645104327879786e-24</v>
+        <v>3.645104327879733e-24</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.3360117637295977</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2684816016281898</v>
+        <v>0.2684816016281894</v>
       </c>
       <c r="D4" t="n">
         <v>1.276750601267726</v>
       </c>
       <c r="E4" t="n">
-        <v>1.871175951139158</v>
+        <v>1.871175951139157</v>
       </c>
       <c r="F4" t="n">
         <v>1.545535761361446</v>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.453607464503556e-08</v>
+        <v>7.453607464503609e-08</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
